--- a/src/physion/acquisition/DataTable.xlsx
+++ b/src/physion/acquisition/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\physion\src\physion\acquisition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6EF13B-9B1C-4D69-891F-62E0BE4FDCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68043FD6-A3C3-4F62-ACA7-C36581715CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="3465" windowWidth="38700" windowHeight="15885" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recordings" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>subject</t>
   </si>
@@ -120,10 +120,13 @@
     <t>protocol</t>
   </si>
   <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Npx-Folder</t>
+  </si>
+  <si>
     <t>Npx-Rec</t>
-  </si>
-  <si>
-    <t>Npx-Folder</t>
   </si>
 </sst>
 </file>
@@ -249,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -268,9 +271,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -486,14 +486,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
     <col min="2" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="6" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="6" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -504,47 +504,47 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>5</v>
+        <v>32</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="M1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F5" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -564,50 +564,50 @@
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:15" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -629,16 +629,16 @@
     <col min="1" max="1" width="19.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
+      <c r="A2" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>

--- a/src/physion/acquisition/DataTable.xlsx
+++ b/src/physion/acquisition/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\physion\src\physion\acquisition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68043FD6-A3C3-4F62-ACA7-C36581715CBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B69485A-C3C6-49B2-8C70-27664C0363FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="3465" windowWidth="38700" windowHeight="15885" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12900" yWindow="4605" windowWidth="38700" windowHeight="15885" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recordings" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>subject</t>
   </si>
@@ -39,9 +39,6 @@
     <t>time</t>
   </si>
   <si>
-    <t>FOV</t>
-  </si>
-  <si>
     <t>force_to_visualStimTimestamps</t>
   </si>
   <si>
@@ -63,12 +60,6 @@
     <t>raw_FaceCamera</t>
   </si>
   <si>
-    <t>processed_CaImaging</t>
-  </si>
-  <si>
-    <t>raw_CaImaging</t>
-  </si>
-  <si>
     <t>max_episode</t>
   </si>
   <si>
@@ -121,12 +112,6 @@
   </si>
   <si>
     <t>Location</t>
-  </si>
-  <si>
-    <t>Npx-Folder</t>
-  </si>
-  <si>
-    <t>Npx-Rec</t>
   </si>
 </sst>
 </file>
@@ -486,14 +471,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
     <col min="2" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="6" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="6" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -504,46 +489,31 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -569,46 +539,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -631,10 +601,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">

--- a/src/physion/acquisition/DataTable.xlsx
+++ b/src/physion/acquisition/DataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\physion\src\physion\acquisition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B69485A-C3C6-49B2-8C70-27664C0363FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FA8BB1-30EA-4343-9AB3-D91EF1425403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="4605" windowWidth="38700" windowHeight="15885" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="38700" windowHeight="15885" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recordings" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>subject</t>
   </si>
@@ -471,14 +471,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
     <col min="2" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="6" customFormat="1" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,31 +488,34 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
